--- a/Normalization/User.xlsx
+++ b/Normalization/User.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Normalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29896234-EF92-4C12-A5AC-615700F46964}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7CA149-D31E-4A71-BEC2-91D422D3748B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>帳號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,6 +40,14 @@
   </si>
   <si>
     <t>bbb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛新紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aaa</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -103,11 +111,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC6E4E73-91F7-4C1C-B7F6-204C16BACDC8}" name="表格1" displayName="表格1" ref="A1:B3" totalsRowShown="0">
-  <autoFilter ref="A1:B3" xr:uid="{5A911BD0-DA20-4E18-877B-EE27D8565420}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC6E4E73-91F7-4C1C-B7F6-204C16BACDC8}" name="表格1" displayName="表格1" ref="A1:C4" totalsRowShown="0">
+  <autoFilter ref="A1:C4" xr:uid="{5A911BD0-DA20-4E18-877B-EE27D8565420}"/>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DE82E25F-8A37-4A67-AEF3-1CF9A5B27771}" name="帳號"/>
     <tableColumn id="2" xr3:uid="{77796192-C653-4C85-AF58-27A0F34C1DFA}" name="密碼"/>
+    <tableColumn id="3" xr3:uid="{4F2440E2-54A4-469F-87B5-81FC12F34F75}" name="愛新紀錄"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -376,31 +385,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>922</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1111</v>
       </c>
     </row>
   </sheetData>
